--- a/arkusz_oceniania BENC KACPER.xlsx
+++ b/arkusz_oceniania BENC KACPER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrric\Desktop\OZE PROJEKT BENC KACPER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC5BA2E-AE01-4C0E-93D3-312CB5CB48F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4740D620-77A2-4173-90E3-6AEED49A18E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Data oceny:</t>
   </si>
   <si>
-    <t>Repozytorium/link:</t>
-  </si>
-  <si>
     <t>Wersja oddania:</t>
   </si>
   <si>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>Grupa: 2</t>
+  </si>
+  <si>
+    <t>Repozytorium/link: https://github.com/KacperBenc/PROJEKT-OZE</t>
   </si>
 </sst>
 </file>
@@ -371,6 +371,21 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -379,21 +394,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -576,26 +576,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1">
       <c r="A3" s="6"/>
@@ -606,22 +606,22 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="138">
+    <row r="4" spans="1:7" ht="120.75">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>69</v>
+      <c r="F4" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="G4" s="6"/>
     </row>
@@ -631,14 +631,14 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5" s="6"/>
     </row>
@@ -653,7 +653,7 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -664,16 +664,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
       <c r="A8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="13" t="s">
         <v>10</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>11</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
@@ -684,102 +684,102 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="42.75">
       <c r="A10" s="1">
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" ht="42.75">
       <c r="A11" s="1">
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" spans="1:7" ht="28.5">
       <c r="A12" s="1">
         <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" spans="1:7" ht="42.75">
       <c r="A13" s="1">
         <v>5</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" ht="21" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:7" ht="21" customHeight="1">
-      <c r="A14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="10" t="str">
+      <c r="B14" s="15" t="str">
         <f>IF(COUNTIF(C9:C13,"NIE")&gt;0,"NIE - projekt wymaga poprawy przed oceną punktową","TAK - można oceniać punktowo")</f>
         <v>TAK - można oceniać punktowo</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10" t="str">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15" t="str">
         <f>IF(COUNTIF(C9:C13,"NIE")&gt;0,"NIE - projekt wymaga poprawy przed oceną punktową","TAK - można oceniać punktowo")</f>
         <v>TAK - można oceniać punktowo</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1">
       <c r="A15" s="6"/>
@@ -792,7 +792,7 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -803,25 +803,25 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="G17" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="48.95" customHeight="1">
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="D18" s="1">
         <v>15</v>
@@ -848,10 +848,10 @@
         <v>2</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -867,10 +867,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="D20" s="1">
         <v>12</v>
@@ -886,10 +886,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="D21" s="1">
         <v>12</v>
@@ -905,10 +905,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="D22" s="1">
         <v>10</v>
@@ -924,10 +924,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="D23" s="1">
         <v>15</v>
@@ -943,10 +943,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="D24" s="1">
         <v>8</v>
@@ -962,10 +962,10 @@
         <v>8</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="D25" s="1">
         <v>12</v>
@@ -981,10 +981,10 @@
         <v>9</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="D26" s="1">
         <v>8</v>
@@ -1005,12 +1005,12 @@
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="A28" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
       <c r="E28" s="3">
         <f>SUM(E18:E26)</f>
         <v>91</v>
@@ -1022,12 +1022,12 @@
       <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1">
-      <c r="A29" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
+      <c r="A29" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
       <c r="E29" s="4">
         <f>E28/100</f>
         <v>0.91</v>
@@ -1039,12 +1039,12 @@
       <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+      <c r="A30" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="3" t="str">
         <f>IF(COUNTIF(C9:C13,"NIE")&gt;0,"warunki min. niespełnione",IF(E28&lt;60,"2,0",IF(E28&lt;68,"3,0",IF(E28&lt;76,"3,5",IF(E28&lt;83,"4,0",IF(E28&lt;90,"4,5","5,0"))))))</f>
         <v>5,0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="32" spans="1:7" ht="15">
       <c r="A32" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -1077,13 +1077,13 @@
     </row>
     <row r="33" spans="1:7" ht="30">
       <c r="A33" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>49</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -1092,93 +1092,93 @@
     </row>
     <row r="34" spans="1:7" ht="28.5">
       <c r="A34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7" ht="28.5">
       <c r="A39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1">
       <c r="A40" s="6"/>
@@ -1191,16 +1191,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="C39:G39"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="D14:G14"/>
@@ -1214,6 +1204,16 @@
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="C33:G33"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D9:G9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C9:C13" xr:uid="{00000000-0002-0000-0000-000000000000}">
